--- a/Team_17/Team Members Details.xlsx
+++ b/Team_17/Team Members Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Malini S\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AA9E2F1-D000-4C37-8A01-B998210480C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DBB96A9-CA72-405F-BF29-31B4B3B28275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>Full Name</t>
   </si>
@@ -128,13 +128,31 @@
   </si>
   <si>
     <t>86,71,8.5</t>
+  </si>
+  <si>
+    <t>https://github.com/madhan-init/schema-aware-data-generator</t>
+  </si>
+  <si>
+    <t>https://github.com/madhan-init</t>
+  </si>
+  <si>
+    <t>https://github.com/gokubuilds</t>
+  </si>
+  <si>
+    <t>https://github.com/maliniaids-stack</t>
+  </si>
+  <si>
+    <t>https://github.com/Manisha0597</t>
+  </si>
+  <si>
+    <t>Project GitHub Repository Link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +188,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +205,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -202,11 +228,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -218,9 +312,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -241,8 +332,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -456,25 +566,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1000"/>
+  <dimension ref="A1:Y1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="27.88671875" customWidth="1"/>
     <col min="4" max="4" width="40.109375" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" style="8" customWidth="1"/>
     <col min="6" max="6" width="13.109375" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="31.77734375" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" customWidth="1"/>
-    <col min="11" max="11" width="28.88671875" customWidth="1"/>
-    <col min="12" max="12" width="43.21875" customWidth="1"/>
-    <col min="13" max="13" width="43.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.33203125" customWidth="1"/>
-    <col min="15" max="24" width="8.6640625" customWidth="1"/>
+    <col min="7" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="31.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.21875" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="28.88671875" customWidth="1"/>
+    <col min="13" max="13" width="43.21875" customWidth="1"/>
+    <col min="14" max="14" width="43.6640625" customWidth="1"/>
+    <col min="15" max="15" width="41.33203125" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" customWidth="1"/>
+    <col min="17" max="25" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -487,7 +598,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -496,31 +607,33 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -529,52 +642,57 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>7358317933</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="6">
+      <c r="K2" s="5">
         <v>83</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="5">
         <v>8.5</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -583,147 +701,157 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6">
+      <c r="B3" s="11"/>
+      <c r="C3" s="5">
         <v>9003099388</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6">
+      <c r="H3" s="15"/>
+      <c r="I3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="5">
         <v>89.2</v>
       </c>
-      <c r="J3" s="6">
+      <c r="K3" s="5">
         <v>84.6</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="5">
         <v>7.8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="P3" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6">
+      <c r="B4" s="11"/>
+      <c r="C4" s="5">
         <v>7010524655</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="5">
         <v>75</v>
       </c>
-      <c r="K4" s="6">
+      <c r="L4" s="5">
         <v>87</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="P4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6">
+      <c r="B5" s="11"/>
+      <c r="C5" s="5">
         <v>9176335591</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6">
+      <c r="H5" s="16"/>
+      <c r="I5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="5">
         <v>86</v>
       </c>
-      <c r="J5" s="6">
+      <c r="K5" s="5">
         <v>71</v>
       </c>
-      <c r="K5" s="6">
+      <c r="L5" s="5">
         <v>8.5</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="P5" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1713,6 +1841,13 @@
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="H2:H5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{CD122EAB-FBC4-4CAD-9AC8-F9881E10C676}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{D8AD7530-D407-4575-9446-60E63EEADBF6}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{3C2B7233-F54D-4C17-940A-85FD0C629027}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{A8A6E4CE-2736-4438-85B1-4ABC8551883B}"/>
+    <hyperlink ref="I5" r:id="rId5" xr:uid="{9FED8B88-F416-45DD-9D23-19770172DD2C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
